--- a/data/aliments.xlsx
+++ b/data/aliments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\OneDrive\Documents\GitHub\Orava\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A2180-BEF5-4EF4-861F-8D50F36279EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655A6B93-5261-42DA-B7A1-AF0435C69446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9DF677CB-CDE3-4AF1-8B1E-695B0A3AAC34}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="74">
   <si>
     <t>nom</t>
   </si>
   <si>
-    <t>saison</t>
-  </si>
-  <si>
     <t>Poulet</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
     <t xml:space="preserve">Courgette </t>
   </si>
   <si>
-    <t>Pois chiches</t>
-  </si>
-  <si>
     <t>Poivron</t>
   </si>
   <si>
@@ -188,9 +182,6 @@
     <t>Concentré de tomate</t>
   </si>
   <si>
-    <t>Fromage pâte préssée</t>
-  </si>
-  <si>
     <t>Parmesan</t>
   </si>
   <si>
@@ -200,21 +191,12 @@
     <t>id</t>
   </si>
   <si>
-    <t>protéine animale</t>
-  </si>
-  <si>
-    <t>protéine végétale</t>
-  </si>
-  <si>
     <t>fct_1</t>
   </si>
   <si>
     <t>fct_2</t>
   </si>
   <si>
-    <t>féculent, légume, fruit,  protéine animale, protéine végétale, sucrerie, sauce</t>
-  </si>
-  <si>
     <t>fruit</t>
   </si>
   <si>
@@ -230,19 +212,52 @@
     <t>sucrerie</t>
   </si>
   <si>
-    <t>féculent</t>
-  </si>
-  <si>
-    <t>légume</t>
-  </si>
-  <si>
-    <t>sauce</t>
-  </si>
-  <si>
-    <t>protéine, féculent, sucre_rapide, légume, autre</t>
-  </si>
-  <si>
-    <t>céréale, fruit, légume, viande, laitier, sucrerie, autre</t>
+    <t>amidon</t>
+  </si>
+  <si>
+    <t>legume</t>
+  </si>
+  <si>
+    <t>viande</t>
+  </si>
+  <si>
+    <t>laitier</t>
+  </si>
+  <si>
+    <t>Fromage</t>
+  </si>
+  <si>
+    <t>Pesto</t>
+  </si>
+  <si>
+    <t>autre</t>
+  </si>
+  <si>
+    <t>proteine</t>
+  </si>
+  <si>
+    <t>feculent</t>
+  </si>
+  <si>
+    <t>Patate douce</t>
+  </si>
+  <si>
+    <t>sucre_rapide</t>
+  </si>
+  <si>
+    <t>principal</t>
+  </si>
+  <si>
+    <t>secondaire</t>
+  </si>
+  <si>
+    <t>plat</t>
+  </si>
+  <si>
+    <t>tout</t>
+  </si>
+  <si>
+    <t>collation</t>
   </si>
 </sst>
 </file>
@@ -628,631 +643,1234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B386388-A7D9-4B3E-89C4-7A29C935A474}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1"/>
     <col min="2" max="2" width="22.81640625" style="1" customWidth="1"/>
     <col min="3" max="7" width="23.1796875" style="1" customWidth="1"/>
     <col min="8" max="10" width="10.90625" style="1"/>
-    <col min="11" max="11" width="78" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" style="1" customWidth="1"/>
     <col min="12" max="16384" width="10.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>49</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
+        <v>50</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
+        <v>51</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
+        <v>52</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
+        <v>53</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>65</v>
+      <c r="E53" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
